--- a/data.xlsx
+++ b/data.xlsx
@@ -5,19 +5,20 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Wheelset" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Tires" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Discs" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Shifters" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Derailleurs" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="Cassette" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Tyres" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Cockpit" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Tape" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Saddle" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Shifters" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="Crankset" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="Saddle" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="Cockpit" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Derailleurs" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Cassette" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Discs" sheetId="11" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="81">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -46,7 +47,13 @@
     <t xml:space="preserve">ImageURL</t>
   </si>
   <si>
-    <t xml:space="preserve">ZIndex</t>
+    <t xml:space="preserve">Zindex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardimg</t>
   </si>
   <si>
     <t xml:space="preserve">S-Works Tarmac SL8</t>
@@ -58,6 +65,9 @@
     <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/Frame.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Madone SLR Gen 7</t>
   </si>
   <si>
@@ -76,7 +86,10 @@
     <t xml:space="preserve">ENVE</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/WheelO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/wheel.png</t>
   </si>
   <si>
     <t xml:space="preserve">BLACK INC</t>
@@ -88,6 +101,9 @@
     <t xml:space="preserve">ZIPP</t>
   </si>
   <si>
+    <t xml:space="preserve">ENVE Foundation</t>
+  </si>
+  <si>
     <t xml:space="preserve">GP5000</t>
   </si>
   <si>
@@ -97,19 +113,166 @@
     <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/GP500.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRO ONE</t>
   </si>
   <si>
     <t xml:space="preserve">Schwalbe</t>
   </si>
   <si>
+    <t xml:space="preserve">GP5000 TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO ONE TLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 90-420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 90-400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 100-420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 110-420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 GRIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIZARD SKIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/lizard-skins-dsp-bar-tape-v2-2.5mm-369874-12.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 FLOUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/lizard-skins-dsp-bar-tape-v2-2.5mm-369874-17.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 GREEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/LZSGR.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selle Italia 142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/Saddle.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prologo 142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fizik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Rival E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/ForceE1Shift.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram RED E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS E1 48/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/ForceE1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Rival AXS E1 48/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram RED AXS E1 48/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/AXSRDE1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Red AXS E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Rival AXS E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS 10-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/Sram_Red.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS 10-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS 10-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">CENTERLINE</t>
   </si>
   <si>
     <t xml:space="preserve">SRAM</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/DiscsOO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/DISCSRAM.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTERLINE FORCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTERLINE RED</t>
   </si>
 </sst>
 </file>
@@ -119,7 +282,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -151,6 +314,14 @@
     </font>
     <font>
       <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -200,7 +371,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -217,7 +388,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -238,7 +417,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
@@ -266,13 +445,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>5500</v>
@@ -281,18 +466,21 @@
         <v>685</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>5200</v>
@@ -301,18 +489,21 @@
         <v>750</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>6000</v>
@@ -321,17 +512,23 @@
         <v>770</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="H2" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/Frame.png"/>
+    <hyperlink ref="E3" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="H3" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/Frame.png"/>
+    <hyperlink ref="E4" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="H4" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/Frame.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -348,14 +545,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -368,14 +566,219 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>168</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -391,7 +794,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -418,13 +821,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -432,19 +841,22 @@
       <c r="D2" s="0" t="n">
         <v>1250</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
+      <c r="E2" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -452,19 +864,22 @@
       <c r="D3" s="0" t="n">
         <v>1350</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
+      <c r="E3" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -472,14 +887,46 @@
       <c r="D4" s="0" t="n">
         <v>1450</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>1399</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -495,7 +942,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -522,13 +969,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -536,19 +989,22 @@
       <c r="D2" s="0" t="n">
         <v>520</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>21</v>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -556,17 +1012,68 @@
       <c r="D3" s="0" t="n">
         <v>499</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>21</v>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>560</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>550</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -583,12 +1090,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -610,28 +1116,161 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>80</v>
+        <v>499</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>320</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
+        <v>185</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+    <hyperlink ref="H3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+    <hyperlink ref="H4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+    <hyperlink ref="H5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+    <hyperlink ref="H6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+    <hyperlink ref="H7" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+    <hyperlink ref="H8" r:id="rId7" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+    <hyperlink ref="H9" r:id="rId8" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/BLACKINCBAR.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -647,13 +1286,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.99"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,20 +1306,82 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/lizard-skins-dsp-bar-tape-v2-2.5mm-369874-12.png"/>
+    <hyperlink ref="H3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/lizard-skins-dsp-bar-tape-v2-2.5mm-369874-17.png"/>
+    <hyperlink ref="H4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/LZSGR.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -689,13 +1391,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,14 +1410,142 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -731,13 +1561,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,14 +1580,94 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>399</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>390</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>599</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -773,13 +1683,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,14 +1705,94 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>799</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>999</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -815,13 +1808,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -834,14 +1828,94 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>449</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>349</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>490</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
